--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -1,80 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Modules"/>
-    <sheet r:id="rId2" sheetId="2" name="UC BPMN"/>
-    <sheet r:id="rId3" sheetId="3" name="UC Non-BPMN"/>
-    <sheet r:id="rId4" sheetId="4" name="Entities"/>
+    <sheet name="Modules" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UC BPMN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UC Non-BPMN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Entities" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
-  <si>
-    <t>Entity yang dibutuhkan</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>ERD</t>
-  </si>
-  <si>
-    <t>Kode</t>
-  </si>
-  <si>
-    <t>Nama Use Case</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Modul</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Deskripsi</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t>Entity/Objek Terkait</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFd9d9d9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,34 +79,102 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -427,27 +462,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="2" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="16.005" customWidth="1" bestFit="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="16" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="70" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Modul</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Sub Modul</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Deskripsi</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Master atribut produk: Jenis Produk, Jenis Sertifikasi, Jenis Bidang, Varian Pelaksanaan</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Produk</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Product Combine (menghasilkan Paket Produk) dan Katalog Produk</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Master Peserta (customer Public) dan Master Company (customer B2B)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Master Rate: item Fixed Cost &amp; Variable Cost dengan Default Cost dan Mode Harga</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Master Program: Paket Produk + costing baseline (tanpa Public/B2B, tanpa customer); Draft -&gt; Final / Batal</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-MP-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program Public / B2B dari Master Program Final: tanggal, lokasi, harga (B2B per peserta atau all-in, diskon), costing; Draft -&gt; Final (Public ke Quotation, B2B ke Sales Order) / Batal</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Quotation dari Penjualan Program Final (Public &amp; B2B; Sales Order tidak ada): tujuan Company/Personal, peserta, skema harga per peserta / all-in (B2B), diskon Rupiah, Keterangan, Formulir Konfirmasi (Public), cetak PDF, Deal/Batal per peserta, Confirmation Letter (Public)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Semua pergerakan data di sistem (tambah, edit, hapus, aktif/nonaktif, finalkan, batalkan, kirim &amp; cetak, deal, cetak) dengan pengguna, tanggal &amp; jam, dan field sebelum → sesudah; kolom jejak Dibuat/Diubah di semua daftar</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -456,156 +690,1520 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="5" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="28.005" customWidth="1" bestFit="1"/>
+    <col width="10" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="26" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="14" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="30" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
+    <col width="70" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
+    <col width="30" bestFit="1" customWidth="1" style="5" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Kode</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Nama Use Case</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Modul</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Sub Modul</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Deskripsi</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Entity/Objek Terkait</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1"/>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customHeight="1"/>
+    <row r="7" ht="18.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="2" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="2" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="2" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="2" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="2" width="28.005" customWidth="1" bestFit="1"/>
+    <col width="10" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="26" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="14" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="16" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="16" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="30" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="70" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="30" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Kode</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Nama Use Case</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Modul</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Sub Modul</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Deskripsi</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Entity/Objek Terkait</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>UC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Jenis Produk</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Nama Jenis Produk</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Aktor membuka daftar Jenis Produk, menambah data baru (kode dibuat sistem), mengubah, atau mengaktifkan/menonaktifkan data. Data tidak dapat dihapus.</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Data Jenis Produk tersimpan dengan kode otomatis dan status</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Jenis Produk</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>FR-03, FR-04, FR-08, FR-09, FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>UC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Jenis Sertifikasi</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Nama Jenis Sertifikasi</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Sama dengan UC-01 untuk master Jenis Sertifikasi.</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Data Jenis Sertifikasi tersimpan dengan kode otomatis dan status</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Jenis Sertifikasi</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>FR-03, FR-05, FR-08, FR-09, FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>UC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Jenis Bidang</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Nama Jenis Bidang</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Sama dengan UC-01 untuk master Jenis Bidang. Jenis Bidang juga menjadi pilihan Bidang pada Master Peserta.</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Data Jenis Bidang tersimpan dengan kode otomatis dan status</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Jenis Bidang</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>FR-03, FR-06, FR-08, FR-09, FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>UC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Varian Pelaksanaan</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Nama Varian</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Sama dengan UC-01 untuk master Varian Pelaksanaan.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Data Varian Pelaksanaan tersimpan dengan kode otomatis dan status</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Varian Pelaksanaan</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>FR-03, FR-07, FR-08, FR-09, FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>UC-05</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Menyusun Product Combine</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Produk</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Judul; satu atau lebih baris kombinasi Produk + Bidang + Varian + Sertifikasi</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Aktor mengisi Judul secara manual, menambah baris kombinasi, memilih keempat atribut aktif per baris, menghapus baris yang tidak perlu, lalu menyimpan. Sistem menolak kombinasi yang keempat atributnya sama persis dengan paket lain atau baris lain. Setiap baris disimpan sebagai satu Paket Produk dengan Nomor Product Combine sendiri.</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Satu Paket Produk per baris, berstatus aktif, tampil di daftar</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk, Jenis Produk, Jenis Sertifikasi, Jenis Bidang, Varian Pelaksanaan</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>FR-01, FR-02, FR-10 – FR-13, FR-22 – FR-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>UC-06</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Menghasilkan Katalog Produk</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Produk</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk aktif</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Ditunda — format katalog belum ada. Sistem menyusun katalog dari Paket Produk.</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Katalog Produk</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk, Katalog Produk</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>FR-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>UC-07</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Peserta</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Nama, Gender, Instansi, Bidang, Provinsi, Kota/Kabupaten, No Telp/WA, Email (semua wajib)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Aktor menambah peserta lewat form (Kota/Kabupaten tersaring menurut Provinsi), mengubah, atau menghapus peserta dari daftar. Peserta menjadi customer penjualan Public dan dipilih di modul Quotation (ditunda).</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Data Peserta tersimpan dengan Kode Peserta</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Peserta, Jenis Bidang, Provinsi, Kota/Kabupaten</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>FR-15 – FR-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>UC-08</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Item Variable Cost</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Item, Kategori (Variable), Satuan (Peserta/Event atau Peserta/Day), Default Cost, Keterangan, COA</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Aktor membuka tab Variable Cost pada Master Rate, menambah item (kode dibuat sistem), mengubah, atau mengaktifkan/menonaktifkan item. Item tidak dapat dihapus. Pilihan Satuan hanya Peserta/Event dan Peserta/Day.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Item Variable Cost tersimpan dengan kode otomatis, Default Cost, dan status</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Rate Variable Cost, Satuan, COA</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>FR-18, FR-19, FR-25, FR-33 – FR-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>UC-09</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Item Fixed Cost</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Item, Kategori (Fixed), Satuan (Event atau Day), Default Cost, Keterangan, COA</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Sama dengan UC-08 pada tab Fixed Cost. Pilihan Satuan hanya Event dan Day.</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Item Fixed Cost tersimpan dengan kode otomatis, Default Cost, dan status</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Rate Fixed Cost, Satuan, COA</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>FR-18, FR-20, FR-25, FR-33 – FR-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>UC-10</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Mengaktifkan / Menonaktifkan Paket Produk</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Produk</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk terpilih</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih paket pada daftar lalu mengubah statusnya menjadi aktif atau nonaktif.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Status Paket Produk berubah</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>FR-10, FR-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>UC-11</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Mencatat Company</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Nama, Jenis Instansi, Alamat, Provinsi, Kota, Telepon &amp; Email kantor, PIC (Nama, Jabatan, Telp/WA, Email) — semua wajib; NPWP opsional</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Aktor menambah company lewat form, mengubah, atau menghapus company dari daftar. Company menjadi customer penjualan B2B dan dipilih saat membuat Penjualan Program B2B.</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Data Company tersimpan dengan Kode Company</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Company, Provinsi, Kota/Kabupaten</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>FR-30 – FR-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>UC-19</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Menyusun Master Program</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-MP-01)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk aktif, Durasi (hari), Target peserta (default 10, dapat diedit), Harga jual standar / peserta, Target profit (opsional), nominal item Fixed &amp; Variable Cost, biaya manual</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih Paket Produk dan mengisi angka baseline. Sistem menampilkan semua item Fixed Cost aktif dengan Default Cost; aktor menghapus (×) item yang tidak dipakai, menyesuaikan nominal bila perlu, menambah item Variable Cost satu per satu, dan bila perlu biaya manual di luar master. Simulasi (Total Fixed, Total Variable, HPP, Profit, Harga BEP / peserta, Jumlah peserta BEP) dihitung ulang setiap angka berubah. Aktor menyimpan sebagai Draft dan dapat mengubahnya lagi selama Draft.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Master Program berstatus Draft dengan Nomor Master Program, costing, dan simulasi</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Master Program, Biaya Master Program, Paket Produk, Rate Fixed Cost, Rate Variable Cost, Satuan</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>MP-FR-01 – MP-FR-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>UC-20</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Memfinalkan Master Program</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-MP-01)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Master Program berstatus Draft</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Aktor menekan "Finalkan program". Sistem menampilkan popup ringkasan (durasi, target peserta, harga jual, HPP, profit, BEP) dan peringatan bila profit minus atau BEP di atas target. Setelah dikonfirmasi status menjadi Final tanpa berpindah halaman; program terkunci dan muncul sebagai pilihan di Penjualan Program.</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Master Program Final, terkunci, tersedia di Penjualan Program</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>MP-FR-11 – MP-FR-13, MP-FR-15, MP-FR-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>UC-21</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Membatalkan Master Program</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-MP-01)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Master Program berstatus Draft atau Final</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih Batalkan dan mengonfirmasi. Status menjadi Batal; program tidak muncul lagi di pilihan Penjualan Program. Penjualan Program yang sudah terbentuk dari program ini tidak terpengaruh.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Master Program berstatus Batal</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>MP-FR-11, MP-FR-14, MP-FR-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>UC-22</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Menyusun Penjualan Program</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Master Program Final, jenis (Public / B2B), tanggal &amp; lokasi acara, durasi, target peserta, harga jual / peserta, target profit, costing</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih Master Program Final dan jenis Public atau B2B. Sistem menyalin durasi, target peserta, harga jual standar, target profit, dan costing dari Master Program. Aktor mengisi tanggal &amp; lokasi, menyesuaikan angka dan item biaya (semua nominal dapat diedit, termasuk biaya lain). Form dan simulasi sama untuk kedua jenis; simulasi dihitung ulang setiap angka berubah. Aktor menyimpan sebagai Draft.</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program Draft dengan Nomor Penjualan</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program, Biaya Penjualan Program, Master Program, Rate Fixed Cost, Rate Variable Cost, Satuan</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>PJ-FR-01 – PJ-FR-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>UC-30</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Mencetak Surat Penawaran</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program berstatus Final</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Aktor membuka Penjualan Program Final dan menekan "Cetak Surat Penawaran". Sistem menampilkan surat penawaran dari angka Final untuk dicetak.</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Surat penawaran</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>PJ-FR-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>UC-31</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Melihat Laporan Rencana vs Aktual</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Laporan</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program Final, peserta fix dari Quotation</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Aktor membuka laporan dan memilih penjualan / periode. Sistem menampilkan rencana, aktual, dan selisih (peserta, pendapatan, HPP, profit).</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Laporan Rencana vs Aktual</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program, Biaya Penjualan Program</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>PJ-FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Membatalkan Penjualan Program</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program berstatus Draft</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih Batalkan dan mengonfirmasi. Status menjadi Batal dan tidak dapat diubah.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program berstatus Batal</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>PJ-FR-14, PJ-FR-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>UC-29</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Memfinalkan Penjualan Program</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program berstatus Draft</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Aktor menekan "Finalkan". Sistem menampilkan popup ringkasan (jenis, durasi, target peserta, harga jual / peserta, pendapatan, HPP, profit, titik impas) dan peringatan bila profit minus. Setelah dikonfirmasi status menjadi Final dan terkunci; Public dan B2B siap masuk ke Quotation.</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program Final, terkunci</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>PJ-FR-14 – PJ-FR-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>UC-33</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Membuat Quotation</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program Final, tanggal, berlaku sampai, sales (Master User), sumber informasi, tujuan (Company / Personal), Company + u.p. + alamat, peserta (dari Master Peserta atau peserta baru), skema harga (B2B: per peserta / all-in), diskon Rupiah, PPN, biaya lain-lain, Keterangan, Formulir Konfirmasi (Public)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih Penjualan Program Final. Public dapat dibuatkan quotation berkali-kali; B2B satu quotation (selain Batal), tujuan terkunci ke Company penjualan, minimal 10 peserta, skema harga per peserta atau all-in (all-in boleh diskon Rupiah total), tanpa langkah Formulir Konfirmasi. Peserta baru dari form langsung tersimpan di Master Peserta. Aktor melihat Preview PDF lalu menyimpan sebagai Draft.</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Draft dengan nomor LM-I/AM/PW/MM/YY-XXX; peserta baru tersimpan di Master Peserta</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Quotation, Peserta Quotation, Keterangan Quotation, Penjualan Program, Peserta, Company, Master User, Template Keterangan, Template Formulir Konfirmasi</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>QTN-FR-03 – QTN-FR-08, QTN-FR-17 – QTN-FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>UC-34</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Kirim dan Cetak Quotation</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Draft / Terkirim / Deal</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Aktor membuka pratinjau PDF: Penawaran + Syarat &amp; Ketentuan + Formulir Konfirmasi per peserta (B2B tanpa formulir), lalu Kirim &amp; Cetak. Dari Draft status menjadi Terkirim dan terkunci; Terkirim/Deal dapat dicetak ulang.</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>PDF quotation; status Terkirim (menunggu deal)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Quotation, Peserta Quotation, Keterangan Quotation, Peserta</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>QTN-FR-10, QTN-FR-14 – QTN-FR-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>UC-35</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Menandai Deal</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Terkirim</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Aktor mencentang peserta yang deal (default semua, minimal 1; B2B minimal 10). Peserta tidak dicentang menjadi Batal dan bebas dipakai di quotation lain.</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Deal; peserta Deal = peserta aktual (laporan Rencana vs Aktual)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Quotation, Peserta Quotation, Keterangan Quotation</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>QTN-FR-11, QTN-FR-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>UC-36</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Membatalkan Quotation</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Draft / Terkirim</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih Batalkan untuk quotation yang tidak jadi deal dan mengonfirmasi. Status Batal, tidak dapat diubah; pesertanya dapat dibuatkan quotation baru (B2B: quotation baru boleh dibuat).</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Batal</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Quotation, Peserta Quotation, Keterangan Quotation</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>QTN-FR-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>UC-37</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mencetak Confirmation Letter</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Quotation Deal (Public saja)</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Aktor mencetak Formulir Konfirmasi Keikutsertaan untuk peserta Deal sesuai template formulir quotation. Tidak tersedia untuk quotation B2B. Status tidak berubah.</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Formulir Konfirmasi peserta Deal</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Quotation, Peserta Quotation, Keterangan Quotation, Template Formulir Konfirmasi</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>QTN-FR-13, QTN-FR-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>UC-38</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Melihat Activity Log</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen, Admin Developer</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Filter modul, aksi, pengguna, rentang tanggal; kata kunci</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Aktor membuka menu Activity Log. Sistem menampilkan semua pergerakan data terbaru di atas (waktu, pengguna, modul, aksi, data, ringkasan perubahan). Aktor menyaring/mencari lalu membuka Detail untuk melihat field sebelum → sesudah. Catatan tidak dapat diubah atau dihapus. Hanya group Manajemen dan Admin Developer; log disimpan 60 hari lalu dihapus otomatis; login/logout tidak dicatat.</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Daftar Activity Log; detail perubahan</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log, Master User</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>LOG-FR-03 – LOG-FR-06, LOG-FR-08, LOG-FR-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>UC-39</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Melihat riwayat satu data</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen, Admin Developer</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Baris data di daftar mana pun (Master Data, Master Program, Penjualan Program, Quotation)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Aktor memilih menu gear "Lihat Riwayat" pada baris data. Sistem membuka Activity Log yang tersaring ke data itu (dibuat, diubah, status, dihapus). Kolom "Dibuat / Diubah" di daftar menampilkan pembuat dan pengubah terakhir beserta tanggal &amp; jam.</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Riwayat satu data</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log, Master User</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>LOG-FR-01, LOG-FR-02, LOG-FR-07, LOG-FR-09</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -614,27 +2212,824 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="2" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="8.005" customWidth="1" bestFit="1"/>
+    <col width="24" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="16" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Entity yang dibutuhkan</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Modul</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Sub Modul</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>ERD</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Tabel ERD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Jenis Produk</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>ms_jenis_produk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Jenis Sertifikasi</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>ms_jenis_sertifikasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Jenis Bidang</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>ms_jenis_bidang</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Varian Pelaksanaan</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Atribut Produk</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>ms_varian_pelaksanaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Paket Produk</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Produk</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>paket_produk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Katalog Produk</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Produk</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>— (ditunda, FR-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Peserta</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>ms_peserta (+ id_customer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>customer (existing, + jenis_instansi; Q-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Provinsi</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>— (tabel existing)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>provinsi (existing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Kota/Kabupaten</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>— (tabel existing)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>kabupaten (existing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Rate Variable Cost</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>ms_rate (tipe = 'variable')</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Rate Fixed Cost</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-06)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>ms_rate (tipe = 'fixed')</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Satuan</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>— (tabel existing)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>ms_satuan (existing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>COA</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>— (tabel existing)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>coa_master (existing, DB akuntansi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-MP-01)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>master_program</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Biaya Master Program</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Master Program</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-MP-01)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>master_program_biaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>penjualan_program</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Biaya Penjualan Program</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan Program</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>TBD (Q-PJ-02)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>penjualan_program_biaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>quotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Peserta Quotation</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>quotation_peserta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Keterangan Quotation</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>quotation_keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Master User</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Pengguna</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>— (tabel existing)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>employees, users (existing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Template Keterangan</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Dokumen</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>ms_template_keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Template Formulir Konfirmasi</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Dokumen</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ms_template_konfirmasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Activity Log</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Manajemen</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>logs (+ kolom jejak created_/updated_/deleted_ di semua tabel)</t>
+        </is>
       </c>
     </row>
   </sheetData>
